--- a/Output Data Tables/AFAT Outputs/Aggregated Tables/2015/Airline_Cumulative_Financial_Statistics_2015.xlsx
+++ b/Output Data Tables/AFAT Outputs/Aggregated Tables/2015/Airline_Cumulative_Financial_Statistics_2015.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="44" uniqueCount="44">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -178,7 +190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -204,49 +216,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1404,48 +1416,248 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>78574610090</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0.1235</v>
+      </c>
+      <c r="D25" s="0">
+        <v>187.69999999999999</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0.14680000000000001</v>
+      </c>
+      <c r="F25" s="0">
+        <v>222.44</v>
+      </c>
+      <c r="G25" s="0">
+        <v>88875858360</v>
+      </c>
+      <c r="H25" s="0">
+        <v>0.13969999999999999</v>
+      </c>
+      <c r="I25" s="0">
+        <v>212.30000000000001</v>
+      </c>
+      <c r="J25" s="0">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="K25" s="0">
+        <v>251.59999999999999</v>
+      </c>
+      <c r="L25" s="0">
+        <v>265113</v>
+      </c>
+      <c r="M25" s="0">
+        <v>2399030</v>
+      </c>
+      <c r="N25" s="0">
+        <v>108737</v>
+      </c>
+      <c r="O25" s="0">
+        <v>335238</v>
+      </c>
+      <c r="P25" s="0">
+        <v>22.059999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>26162063840</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0.1074</v>
+      </c>
+      <c r="D26" s="0">
+        <v>97.129999999999995</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0.12820000000000001</v>
+      </c>
+      <c r="F26" s="0">
+        <v>119.38</v>
+      </c>
+      <c r="G26" s="0">
+        <v>32631067630</v>
+      </c>
+      <c r="H26" s="0">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="I26" s="0">
+        <v>121.14</v>
+      </c>
+      <c r="J26" s="0">
+        <v>0.15989999999999999</v>
+      </c>
+      <c r="K26" s="0">
+        <v>148.90000000000001</v>
+      </c>
+      <c r="L26" s="0">
+        <v>78961</v>
+      </c>
+      <c r="M26" s="0">
+        <v>3084187</v>
+      </c>
+      <c r="N26" s="0">
+        <v>127600</v>
+      </c>
+      <c r="O26" s="0">
+        <v>413256</v>
+      </c>
+      <c r="P26" s="0">
+        <v>24.170000000000002</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>4388524410</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0.085099999999999995</v>
+      </c>
+      <c r="D27" s="0">
+        <v>85.060000000000002</v>
+      </c>
+      <c r="E27" s="0">
+        <v>0.10009999999999999</v>
+      </c>
+      <c r="F27" s="0">
+        <v>100.69</v>
+      </c>
+      <c r="G27" s="0">
+        <v>5285275590</v>
+      </c>
+      <c r="H27" s="0">
+        <v>0.10249999999999999</v>
+      </c>
+      <c r="I27" s="0">
+        <v>102.45</v>
+      </c>
+      <c r="J27" s="0">
+        <v>0.1205</v>
+      </c>
+      <c r="K27" s="0">
+        <v>121.26000000000001</v>
+      </c>
+      <c r="L27" s="0">
+        <v>11820</v>
+      </c>
+      <c r="M27" s="0">
+        <v>4364157</v>
+      </c>
+      <c r="N27" s="0">
+        <v>89596</v>
+      </c>
+      <c r="O27" s="0">
+        <v>447147</v>
+      </c>
+      <c r="P27" s="0">
+        <v>48.710000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>5253102870</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0.085300000000000001</v>
+      </c>
+      <c r="D28" s="0">
+        <v>40.469999999999999</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0.10489999999999999</v>
+      </c>
+      <c r="F28" s="0">
+        <v>50.579999999999998</v>
+      </c>
+      <c r="G28" s="0">
+        <v>5516429260</v>
+      </c>
+      <c r="H28" s="0">
+        <v>0.089499999999999996</v>
+      </c>
+      <c r="I28" s="0">
+        <v>42.5</v>
+      </c>
+      <c r="J28" s="0">
+        <v>0.11020000000000001</v>
+      </c>
+      <c r="K28" s="0">
+        <v>53.109999999999999</v>
+      </c>
+      <c r="L28" s="0">
+        <v>38513</v>
+      </c>
+      <c r="M28" s="0">
+        <v>1599709</v>
+      </c>
+      <c r="N28" s="0">
+        <v>63533</v>
+      </c>
+      <c r="O28" s="0">
+        <v>143236</v>
+      </c>
+      <c r="P28" s="0">
+        <v>25.18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>114378301210</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>0.1152</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>131.56</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>0.13719999999999999</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>158.88999999999999</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>132308630840</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>0.1333</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>152.19</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>0.1588</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>183.80000000000001</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>394407</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>2517041</v>
       </c>
-      <c r="N25" s="0">
+      <c r="N29" s="0">
         <v>107525</v>
       </c>
-      <c r="O25" s="0">
+      <c r="O29" s="0">
         <v>335462</v>
       </c>
-      <c r="P25" s="0">
+      <c r="P29" s="0">
         <v>23.41</v>
       </c>
     </row>
